--- a/Регистрация2.xlsx
+++ b/Регистрация2.xlsx
@@ -498,7 +498,7 @@
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
     <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="16.140625" customWidth="1"/>
